--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_FC BARCELONA.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_FC BARCELONA.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4.706799999999999</v>
+        <v>3.3599</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6489</v>
+        <v>2.6253</v>
       </c>
       <c r="F2" t="n">
-        <v>1.058</v>
+        <v>0.7347</v>
       </c>
       <c r="G2" t="n">
         <v>9.115400000000001</v>
@@ -610,13 +610,13 @@
         <v>4.776999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5924</v>
+        <v>0.2454</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6287</v>
+        <v>0.605</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03639999999999999</v>
+        <v>-0.3597</v>
       </c>
       <c r="V2" t="n">
         <v>-3.4987</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6243</v>
+        <v>2.962</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5259</v>
+        <v>1.7452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09840000000000004</v>
+        <v>1.2168</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7521</v>
+        <v>2.217</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.72</v>
+        <v>-0.2044</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03210000000000002</v>
+        <v>2.4214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6092</v>
+        <v>3.6339</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8104</v>
+        <v>-0.1781</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4197</v>
+        <v>3.812</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3613</v>
+        <v>-1.4168</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9095</v>
+        <v>-0.02629999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4518</v>
+        <v>-1.3905</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5022</v>
+        <v>1.1374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3648</v>
+        <v>-2.5022</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8671</v>
+        <v>3.6395</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1225</v>
+        <v>-0.5506</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1913</v>
+        <v>0.4553</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9312</v>
+        <v>-1.0059</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2485</v>
+        <v>0.1583</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0901</v>
+        <v>0.1583</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3165</v>
+        <v>1.32</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8346</v>
+        <v>2.184800000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4819</v>
+        <v>-0.8649</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1632</v>
+        <v>2.2451</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4503</v>
+        <v>0.9357999999999997</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7129</v>
+        <v>1.3095</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3776</v>
+        <v>3.9971</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6698</v>
+        <v>2.3254</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7078</v>
+        <v>1.6717</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2142999999999999</v>
+        <v>-1.7518</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2194</v>
+        <v>-1.3897</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005199999999999982</v>
+        <v>-0.3623</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3649</v>
+        <v>0.9099</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5022</v>
+        <v>-3.867</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1373</v>
+        <v>4.776999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2915</v>
+        <v>-0.5867</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5744</v>
+        <v>-0.1254</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2828</v>
+        <v>-0.4613</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7734</v>
+        <v>-1.2485</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6151</v>
+        <v>2.1802</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1583</v>
+        <v>-3.4287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7064999999999997</v>
+        <v>1.2557</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2007999999999996</v>
+        <v>0.9634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5057000000000003</v>
+        <v>0.2923</v>
       </c>
       <c r="G5" t="n">
-        <v>2.217</v>
+        <v>-1.7521</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2044</v>
+        <v>-1.72</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4214</v>
+        <v>-0.03210000000000002</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6339</v>
+        <v>0.6092</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1781</v>
+        <v>-0.8104</v>
       </c>
       <c r="L5" t="n">
-        <v>3.812</v>
+        <v>1.4197</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4168</v>
+        <v>-2.3613</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02629999999999999</v>
+        <v>-0.9095</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3905</v>
+        <v>-1.4518</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1374</v>
+        <v>2.5022</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5022</v>
+        <v>-1.3648</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6395</v>
+        <v>3.8671</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.8062</v>
+        <v>1.754</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0892</v>
+        <v>0.6287999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.717</v>
+        <v>1.1252</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1583</v>
+        <v>-1.2485</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1583</v>
+        <v>1.0901</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3386</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3092000000000001</v>
+        <v>0.6446000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.254</v>
+        <v>0.3888999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5631</v>
+        <v>0.2557</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1691</v>
+        <v>2.1632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03450000000000003</v>
+        <v>1.4503</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2036</v>
+        <v>0.7129</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1516</v>
+        <v>2.3776</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2261</v>
+        <v>1.6698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0745</v>
+        <v>0.7078</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01740000000000001</v>
+        <v>-0.2142999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2606000000000001</v>
+        <v>-0.2194</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2781</v>
+        <v>0.005199999999999982</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9099</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1374</v>
+        <v>-2.5022</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2275</v>
+        <v>1.1373</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6848</v>
+        <v>0.6195999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7184</v>
+        <v>1.1286</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.03360000000000002</v>
+        <v>-0.5091</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7034</v>
+        <v>-0.7734</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3167000000000001</v>
+        <v>-0.6151</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3867</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03039999999999998</v>
+        <v>-0.09759999999999991</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2933</v>
+        <v>-0.1787</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3237</v>
+        <v>0.08089999999999997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3244</v>
+        <v>-0.9387000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5415000000000001</v>
+        <v>1.7129</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8659999999999999</v>
+        <v>-2.6516</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7476</v>
+        <v>0.315</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9531000000000001</v>
+        <v>1.7598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7945</v>
+        <v>-1.4447</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4231</v>
+        <v>-1.2537</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4946</v>
+        <v>-0.0469</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07150000000000001</v>
+        <v>-1.2068</v>
       </c>
       <c r="P7" t="n">
         <v>0.2275</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6395</v>
+        <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8671</v>
+        <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9553</v>
+        <v>0.6135999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.718</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6733</v>
+        <v>-0.03009999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4768</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3760000000000001</v>
+        <v>-0.2348999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2954</v>
+        <v>-0.6041000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0806</v>
+        <v>0.3692</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9387000000000001</v>
+        <v>-0.1691</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7129</v>
+        <v>0.03450000000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6516</v>
+        <v>-0.2036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.315</v>
+        <v>-0.1516</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7598</v>
+        <v>-0.2261</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4447</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2537</v>
+        <v>-0.01740000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0469</v>
+        <v>0.2606000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2068</v>
+        <v>-0.2781</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2275</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3648</v>
+        <v>0.2275</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3353</v>
+        <v>0.1407</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5269</v>
+        <v>0.3682</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1917</v>
+        <v>-0.2275</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7034</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3167000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6662999999999999</v>
+        <v>-0.5370999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>-1.2711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6047999999999999</v>
+        <v>0.7341</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7519</v>
@@ -1156,13 +1156,13 @@
         <v>1.1374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7208</v>
+        <v>0.8501000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.07169999999999999</v>
+        <v>-0.0716</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7924</v>
+        <v>0.9217</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5451</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8708999999999998</v>
+        <v>-0.6465</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4787000000000003</v>
+        <v>-2.0329</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3497</v>
+        <v>1.3864</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2451</v>
+        <v>0.3244</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9357999999999997</v>
+        <v>-0.5415000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3095</v>
+        <v>0.8659999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9971</v>
+        <v>1.7476</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3254</v>
+        <v>0.9531000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6717</v>
+        <v>0.7945</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7518</v>
+        <v>-1.4231</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3897</v>
+        <v>-1.4946</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3623</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.867</v>
+        <v>-3.6395</v>
       </c>
       <c r="R10" t="n">
-        <v>4.776999999999999</v>
+        <v>3.8671</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7776</v>
+        <v>0.2783</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8315</v>
+        <v>-0.4575</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9460999999999999</v>
+        <v>0.736</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2485</v>
+        <v>-1.4768</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1802</v>
+        <v>0.3166</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4287</v>
+        <v>-1.7936</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4993</v>
+        <v>-1.3179</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.991</v>
+        <v>-0.8743</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5082</v>
+        <v>-0.4436</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9438</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5555</v>
+        <v>-0.3741</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2873</v>
+        <v>-0.1706</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2682</v>
+        <v>-0.2036</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8302</v>
+        <v>-2.4582</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4858</v>
+        <v>-2.4351</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6556000000000001</v>
+        <v>-0.0232</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9753</v>
@@ -1390,13 +1390,13 @@
         <v>2.0472</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.9248000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3829</v>
+        <v>0.6677</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9359000000000001</v>
+        <v>0.2571</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0901</v>
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5232</v>
+        <v>-3.6038</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9479</v>
+        <v>-4.6425</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4246</v>
+        <v>1.0388</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3342</v>
@@ -1468,13 +1468,13 @@
         <v>1.5923</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.644</v>
+        <v>0.2754</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2632</v>
+        <v>0.04219999999999996</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3808</v>
+        <v>0.2333</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0721999999999996</v>
+        <v>0.6461999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.849600000000001</v>
+        <v>-4.131099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.777299999999999</v>
+        <v>4.777200000000001</v>
       </c>
       <c r="G14" t="n">
         <v>3.200000000000003</v>
@@ -1525,7 +1525,7 @@
         <v>6.404500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>9.236400000000001</v>
+        <v>9.2364</v>
       </c>
       <c r="M14" t="n">
         <v>-12.4398</v>
@@ -1534,7 +1534,7 @@
         <v>-4.5948</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.8454</v>
+        <v>-7.845399999999999</v>
       </c>
       <c r="P14" t="n">
         <v>2.2748</v>
@@ -1546,13 +1546,13 @@
         <v>28.4342</v>
       </c>
       <c r="S14" t="n">
-        <v>3.472200000000001</v>
+        <v>4.1905</v>
       </c>
       <c r="T14" t="n">
-        <v>2.995899999999999</v>
+        <v>3.7144</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4761999999999998</v>
+        <v>0.4760999999999997</v>
       </c>
       <c r="V14" t="n">
         <v>-9.019400000000001</v>
